--- a/examples/data/capex/Cases.xlsx
+++ b/examples/data/capex/Cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravi.sarna\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://microsoft-my.sharepoint.com/personal/rphillips_microsoft_com/Documents/Repos/autarch-framework-v0.12.0/examples/data/capex/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F627F9-4EF0-4A65-8FEE-4F243CB8C202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{31F627F9-4EF0-4A65-8FEE-4F243CB8C202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BE7E57B-0BFD-41C6-AFAB-3D9C1D6E03AA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{5C11698B-5C44-46B3-8DB2-36F9F8059B17}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5C11698B-5C44-46B3-8DB2-36F9F8059B17}"/>
   </bookViews>
   <sheets>
     <sheet name="EU" sheetId="1" r:id="rId1"/>
@@ -677,15 +677,13 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -1024,239 +1022,239 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D74EAD23-CEFB-4937-A2FA-9A08D2D9D213}">
   <dimension ref="A1:BX2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:76" s="6" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:76" s="1" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BA1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BB1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BC1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BD1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" s="8" t="s">
+      <c r="BE1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BF1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BG1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BH1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BI1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BK1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BL1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BM1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BN1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BO1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BP1" s="6" t="s">
+      <c r="BP1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BQ1" s="6" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BR1" s="6" t="s">
+      <c r="BR1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BS1" s="6" t="s">
+      <c r="BS1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BT1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="BU1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BV1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="BW1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="BX1" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:76" s="1" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:76" s="1" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>71</v>
       </c>
@@ -1414,16 +1412,67 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70A84B5F-F7EE-4CDB-B951-912C643D1674}">
   <dimension ref="A1:CB23"/>
-  <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="48" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="1"/>
+    <col min="21" max="21" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="48" width="8.7109375" style="1"/>
     <col min="49" max="49" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="73" width="8.7265625" style="1"/>
-    <col min="74" max="74" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="75" max="16384" width="8.7265625" style="1"/>
+    <col min="50" max="53" width="8.7109375" style="1"/>
+    <col min="54" max="54" width="102.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="9" style="1" customWidth="1"/>
+    <col min="61" max="61" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="5" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="6.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="4.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="81" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>93</v>
       </c>
@@ -1665,7 +1714,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C2" s="1">
         <v>112680</v>
       </c>
@@ -1811,7 +1860,7 @@
         <v>99.33</v>
       </c>
     </row>
-    <row r="3" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C3" s="1">
         <v>112680</v>
       </c>
@@ -1951,7 +2000,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C4" s="1">
         <v>112680</v>
       </c>
@@ -2091,7 +2140,7 @@
         <v>2746514</v>
       </c>
     </row>
-    <row r="5" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C5" s="1">
         <v>112680</v>
       </c>
@@ -2225,7 +2274,7 @@
         <v>20.83</v>
       </c>
     </row>
-    <row r="6" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C6" s="1">
         <v>112680</v>
       </c>
@@ -2359,7 +2408,7 @@
         <v>41.61</v>
       </c>
     </row>
-    <row r="7" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C7" s="1">
         <v>112680</v>
       </c>
@@ -2493,7 +2542,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="8" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C8" s="1">
         <v>112680</v>
       </c>
@@ -2627,7 +2676,7 @@
         <v>15.69</v>
       </c>
     </row>
-    <row r="9" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C9" s="1">
         <v>112680</v>
       </c>
@@ -2761,7 +2810,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="10" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C10" s="1">
         <v>112680</v>
       </c>
@@ -2895,7 +2944,7 @@
         <v>12.17</v>
       </c>
     </row>
-    <row r="11" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C11" s="1">
         <v>112680</v>
       </c>
@@ -3029,7 +3078,7 @@
         <v>58.74</v>
       </c>
     </row>
-    <row r="12" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C12" s="1">
         <v>112680</v>
       </c>
@@ -3163,7 +3212,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="13" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C13" s="1">
         <v>112680</v>
       </c>
@@ -3285,7 +3334,7 @@
         <v>617.09</v>
       </c>
     </row>
-    <row r="14" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>147</v>
       </c>
@@ -3404,7 +3453,7 @@
         <v>28805</v>
       </c>
     </row>
-    <row r="15" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>147</v>
       </c>
@@ -3517,7 +3566,7 @@
         <v>5120</v>
       </c>
     </row>
-    <row r="16" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:80" x14ac:dyDescent="0.2">
       <c r="C16" s="1" t="s">
         <v>147</v>
       </c>
@@ -3630,7 +3679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:60" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>147</v>
       </c>
@@ -3743,7 +3792,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="18" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:60" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>147</v>
       </c>
@@ -3856,7 +3905,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:60" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>147</v>
       </c>
@@ -3969,7 +4018,7 @@
         <v>5400</v>
       </c>
     </row>
-    <row r="20" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:60" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>147</v>
       </c>
@@ -4082,7 +4131,7 @@
         <v>6300</v>
       </c>
     </row>
-    <row r="21" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:60" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>147</v>
       </c>
@@ -4195,7 +4244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:60" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>147</v>
       </c>
@@ -4308,7 +4357,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:60" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>147</v>
       </c>
